--- a/slides/board_number.xlsx
+++ b/slides/board_number.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Board number" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -438,15 +438,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kalpa Health · Brief &lt;LETTER&gt; · Group &lt;N&gt;</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+          <t>Kalpa Health · Brief A · Group details to add</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -455,7 +451,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>+127.1%</t>
+          <t>+5.01%</t>
         </is>
       </c>
     </row>
@@ -467,7 +463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>tests on bookings that were collected or no-show, after the identity rule in docs/decisions-log.md</t>
+          <t>H1 booked-test growth, using the one-row-per-booking clean count and test-code rules in the notebook.</t>
         </is>
       </c>
     </row>
@@ -478,7 +474,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>39578</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="6">
@@ -488,7 +484,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>17426</v>
+        <v>435008</v>
       </c>
     </row>
     <row r="7">
@@ -499,7 +495,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>H1 2026 against H1 2025, six cities</t>
+          <t>H1 2026 (456,788 tests) against H1 2025 (435,008 tests), six cities</t>
         </is>
       </c>
     </row>
@@ -511,7 +507,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>plan: +18 percent</t>
+          <t>Plan: +18% growth; plan total 515,740 booked tests</t>
         </is>
       </c>
     </row>
@@ -523,7 +519,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>&lt;one sentence for the board&gt;</t>
+          <t>Booked tests increased by 21,780, from 435,008 in H1 2025 to 456,788 in H1 2026 (+5.01%), below the 18% plan.</t>
         </is>
       </c>
     </row>
@@ -535,7 +531,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>&lt;the one thing that would change the claim&gt;</t>
+          <t>This is booked-test growth under the documented cleaning rules; 2,442 two-day date-anomaly rows and 1,311 rows without a valid test code are excluded from the clean count and have separate sensitivities in the notebook/logs.</t>
         </is>
       </c>
     </row>
@@ -546,7 +542,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>ROUND((B5/B6-1)*100,1)</f>
+        <f>ROUND((B5/B6)*100,2)</f>
         <v/>
       </c>
     </row>
